--- a/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/YAP_DOX_vs_CTRL_fgsea_results.xlsx
+++ b/neuroblastoma/results/RNA-seq/RNA-seq_shRNA_pairwise/YAP_DOX_vs_CTRL_fgsea_results.xlsx
@@ -436,19 +436,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.00385786483127174</v>
+        <v>0.0039519590954491</v>
       </c>
       <c r="C2">
-        <v>0.00900168460630073</v>
+        <v>0.00922123788938124</v>
       </c>
       <c r="D2">
-        <v>0.431707695803346</v>
+        <v>0.407017918923954</v>
       </c>
       <c r="E2">
         <v>-0.596381537868828</v>
       </c>
       <c r="F2">
-        <v>-1.64966668487974</v>
+        <v>-1.66850479798948</v>
       </c>
       <c r="G2">
         <v>55</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.582178217821782</v>
+        <v>0.550403225806452</v>
       </c>
       <c r="C3">
-        <v>0.616632860040568</v>
+        <v>0.58974358974359</v>
       </c>
       <c r="D3">
-        <v>0.0707899094502623</v>
+        <v>0.0745500777420554</v>
       </c>
       <c r="E3">
         <v>-0.335564799844487</v>
       </c>
       <c r="F3">
-        <v>-0.933926780547723</v>
+        <v>-0.942696161477949</v>
       </c>
       <c r="G3">
         <v>56</v>
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.466531440162272</v>
+        <v>0.454724409448819</v>
       </c>
       <c r="C4">
-        <v>0.616632860040568</v>
+        <v>0.58974358974359</v>
       </c>
       <c r="D4">
-        <v>0.0835990603684159</v>
+        <v>0.0833634065110386</v>
       </c>
       <c r="E4">
         <v>-0.293913985624395</v>
       </c>
       <c r="F4">
-        <v>-0.996071265865687</v>
+        <v>-0.991171765517879</v>
       </c>
       <c r="G4">
         <v>194</v>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.08</v>
+        <v>0.0587084148727984</v>
       </c>
       <c r="C5">
-        <v>0.14</v>
+        <v>0.102739726027397</v>
       </c>
       <c r="D5">
-        <v>0.224966093540314</v>
+        <v>0.261663521711573</v>
       </c>
       <c r="E5">
         <v>-0.613465419619574</v>
       </c>
       <c r="F5">
-        <v>-1.42314696484191</v>
+        <v>-1.44600979031776</v>
       </c>
       <c r="G5">
         <v>21</v>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.616632860040568</v>
+        <v>0.58974358974359</v>
       </c>
       <c r="C6">
-        <v>0.616632860040568</v>
+        <v>0.58974358974359</v>
       </c>
       <c r="D6">
-        <v>0.069119845655101</v>
+        <v>0.0699458736501659</v>
       </c>
       <c r="E6">
         <v>-0.392070639064183</v>
       </c>
       <c r="F6">
-        <v>-0.897339317859359</v>
+        <v>-0.913782883589439</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -661,26 +661,26 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.000000000000000000429576461893921</v>
+        <v>0.0000000000000000464843374321408</v>
       </c>
       <c r="C7">
-        <v>0.00000000000000000300703523325744</v>
+        <v>0.000000000000000325390362024985</v>
       </c>
       <c r="D7">
-        <v>1.13308993200902</v>
+        <v>1.06720998682811</v>
       </c>
       <c r="E7">
-        <v>-0.504720227729404</v>
+        <v>-0.490296999632756</v>
       </c>
       <c r="F7">
-        <v>-1.94457242248312</v>
+        <v>-1.88825721485498</v>
       </c>
       <c r="G7">
-        <v>839</v>
+        <v>858</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>APLN; AC112777.1; SH3TC2; TUBAP2; TENT5B; LAMA3; DAW1; NCF2; DNAH5; MIR137HG; CCNT2-AS1; ZNF488; CDC45; CENPM; NIPAL1; UTP11; CCN2; STIL; SH2D5; EDN1; KRT34; ANKRD1; C1QTNF2; AURKB; RN7SL3; KBTBD8; NUP35; CCL2; LMCD1; PDSS1; PPIH; POLR3G; CDC6; SCLY; POLR3K; CDCA2; GFRA1; DUSP1; PSRC1; EXOSC3; QTRT2; PLEKHA7; MAD2L1; KIF2C; MPP4; MAP3K14; MAFF; CENPN; RFLNB; DLC1; SPAG5; MAFK; PRPS1; BNC1; HBEGF; MELK; KLF5; ALPK2; C1orf198; IQCJ-SCHIP1; DDAH1; GADD45B; SNRPD1; PDE5A; CCDC85C; BRI3BP; HACD1; KRT81; CCN1; HAUS8; TUFT1; GSG1; MIR503HG; CDCA3; PRR11; UBASH3B; TEAD4; DOCK2; PRR5L; AMOTL2; CCNB1; PPME1; NUAK2; CARD10; NUF2; KIF4A; MAGOHB; DIAPH3; NABP1; RFWD3; UGCG; MYBL1; GPRC5A; TPX2; PSMD11; TGFB2; CEP55; ORC1; RNF182; LIF; ERCC6L; RFX2; AL590004.3; CDK2; DAB2; NLRP1; CDCA8; MPP6; TROAP; RTKN2; PAWR; KIF23; VPS9D1-AS1; FRMD6; TAF13; FGF1; WDR4; GRPR; NF2; SKP2; SPCS3; MARCHF4; LMNB2; TBC1D31; BYSL; CDKN3; TEDC1; C5orf46; ANKRD13A; LBH; UHRF1; JMJD6; WDR77; Z95118.2; LRP8; TFAM; PLK1; CD3EAP; TUBB6; DUSP5; GPN3; PXDC1; LRR1; H2AZ1; FXN; YRDC; TNFRSF12A; PSG9; PGRMC2; CCNB2; FAM72B; FEN1; MBD2; SNHG12; KRTAP2-3; RRM1; SNRPF; STK40; STK32B; BDKRB1; CDK7; POLR2D; TNFSF18; SEPTIN11; SHCBP1; NTMT1; KIF20B; IL7R; ASF1B; MAP3K7CL; PKP4; LMO7-AS1; CAVIN1; GEMIN4; ERCC2; FGF2; HS6ST1; RCL1; HDDC2; PUS1; UAP1; NCAPH; KRT18; ARHGAP11A; PIMREG; RFC2; POLQ; MT2A; MRPL13; RAB8A; AL353751.1; SNHG3; FSTL1; SCIN; IER3; JADE1; SRSF3; UMPS; HMOX2; RPL22L1; CTIF; VPS53; PDLIM1; NOP16; CDCA5; DFFA; MARCHF3; CRIM1; SHLD3; KIF20A; RACGAP1; TOMM40; AC125807.2; FOSL2; ARHGAP23; CITED2; SKA1; AC027237.5; RASSF2; BCYRN1; BIRC5; GTF2H2; SKA3; THBS1; SNAPC1; PTS; LATS2; TK1; NOLC1; KAZN; VKORC1L1; CDC20; CSRP1; TUBB4B; PIEZO1; AC055839.2; UBE2S; AP000944.5; ATAD3A; ETS1; AFAP1; EBNA1BP2; HSPA4; AURKA; PTTG1; PRKAG2; CORO1C; C3orf52; ATP8B1; ARSJ; RANGAP1; TRIP13; PALMD; EXOSC2; ADAM19; PSME3; MATN2; PRC1; WDR34; NRXN3; NUDCD1; RAB3B; MMS22L; HMCES; SYDE1; MPP5; ARID5B; ALYREF; ZWINT; NME1; SRSF1; COTL1; TXNRD1; GLS; DHFR; THOP1; UBE2C; TLX3; OTUD6B; CUL4B; ENAH; PAK1IP1; CKAP2; ANXA3; TGFBI; CYTOR; POLR1E; AL928654.4; DAZAP1; SRF; RAD23B; PET117; MYC; CIT; DIMT1; MTCL1; DLGAP5; PCID2; LOXL2; NUAK1; CDCA4; HACD2; MRPS17; TUBA1B; NSUN2; SNRPB; SMTN; SLC16A3; FAM207A; NAA15; TLL1; NUP188; FLNC; GRPEL1; ACTN4; HAUS6; HSPA14; PBK; SRSF7; NCAPG2; SNU13; TOE1; EIF2S1; E2F7; H2AX; RIPK2; ZNF469; ACTN1; FBN2; TRAM2; ANLN; TUBA1C; SAMD4A; TUBBP1; PDCD1LG2; HAT1; SLC35F2; HSPD1; NT5DC3; UCK2; CCT4; PM20D2; MRPL14; CCNYL1; NDUFAF2; HJURP; ARHGAP18; PDCD5; PADI2; LSM12; RRS1; CHEK1; HSPE1; EMG1; LTV1; NEK7; UPP1; HCCS; BUB1; MYBBP1A; ZBTB18; TRIM59; CENPO; MAMLD1; ANXA2; KRT80; EIF5A; PHLDA2; ADK; KIFC3; DUSP14; CCDC80; USP53; G3BP1; NDUFAF4; LASP1; STAMBPL1; SLC25A32; IMP4; TMEM237; TACC3; TIMM50; METAP1; ELAVL1; MYO1C; WDR89; ATAD3B; GNAI1; KPNA4; SMS; RGMB; SLC7A5; EPAS1; RECK; TPM1; DDX47; CLCF1; FOSL1; METRNL; IFRD2; PKN3; RBM14; TOM1L2; CAP1; EIF3J; YARS1; BOLA2B; TAGLN2; CAPN2; LRRC59; FSTL3; PIP5K1A; ENO1; RSL1D1; KPNA3; WNT5A; SH3RF1; YARS2; WDR43; ARL13B; PALM2AKAP2; EIF1AX; GNL3; ANXA2P2; MCAM; KNSTRN; LYPD6; TOMM5; MIR22HG; MAK16; FAM83D; CBR3; BCAR3; ME2; TUBB; LMO7; DHCR24; NOP56; BCCIP; NUDC; DNTTIP2; MTMR12; CPA4; SGO2; MYL12B; RAB3IP; SCARB1; WDR62; MAP2K3; DCAF13; FABP5; ADARB1; RANBP1; SMAD3; FAM72D; CYB5B; L3HYPDH; NCAPG; UGDH; SEC14L1; C1QBP; LIMA1; MALT1; UTP18; SDHB; BBS7; FH; TARS3; NUP88; IPO5; PPM1G; NPM1P27; SNRPA1; WDR1; CDC42EP1; PHF19; MICAL2; CCT2; NIFK; KPNA2; CTNNAL1; EPS8; RRM2; RRP9; NOL6; NPM1; SHROOM3; MYL12A; VSIR; ARL4A; DKC1; PTP4A2; C20orf27; LDHA; PUS7; TTC27; NGF; MEST; CYCS; DDX21</t>
+          <t>AL161431.1; APLN; AC112777.1; SH3TC2; TUBAP2; MYOSLID; TENT5B; LAMA3; MTF1; DAW1; RNF144B; C13orf46; TNNC1; NCF2; NPPB; CYP24A1; DNAH5; MIR137HG; CCNT2-AS1; ZNF488; EAF2; CDC45; NIPAL1; PSG2; UTP11; CCN2; AC090409.1; STIL; SH2D5; EDN1; KRT34; ANKRD1; C1QTNF2; WWC2; AURKB; RN7SL3; KBTBD8; NUP35; CCL2; LMCD1; PDSS1; POLR3G; CDC6; SCLY; POLR3K; CDCA2; GFRA1; DUSP1; CENPL; PSRC1; PADI1; EXOSC3; QTRT2; PLEKHA7; MAD2L1; PSG6; KIF2C; GCNT4; MPP4; MAP3K14; MAFF; CENPN; RFLNB; DLC1; SPAG5; RRP7A; MAFK; PCOTH; PRPS1; BNC1; PSG11; HBEGF; MELK; KLF5; NEXN; ALPK2; C1orf198; IQCJ-SCHIP1; DDAH1; GADD45B; SNRPD1; PDE5A; CCDC85C; BRI3BP; HACD1; KRT81; CCN1; HAUS8; TUFT1; GSG1; MIR503HG; CDCA3; PRR11; UBASH3B; TEAD4; PRR5L; AMOTL2; CCNB1; PPME1; NUAK2; NUF2; KIF4A; MAGOHB; DIAPH3; NABP1; RFWD3; UGCG; MYBL1; DEPDC1; GPRC5A; TPX2; PSMD11; TGFB2; CEP55; ORC1; LIF; ERCC6L; AL590004.3; CDK2; DAB2; NLRP1; CRYAB; CDCA8; MPP6; TROAP; RTKN2; PAWR; KIF23; VPS9D1-AS1; ADRB2; FRMD6; TAF13; FGF1; WDR4; GRPR; NF2; SKP2; SPCS3; MARCHF4; LMNB2; TBC1D31; BYSL; MNS1; CDKN3; TEDC1; C5orf46; ANKRD13A; LBH; UHRF1; JMJD6; KCTD4; WDR77; Z95118.2; LRP8; TFAM; PLK1; CD3EAP; TUBB6; SHB; DUSP5; KRT33B; PXDC1; LRR1; H2AZ1; FXN; TNFRSF12A; PSG9; PGRMC2; CCNB2; FAM72B; LINC02535; FEN1; MBD2; SNHG12; KRTAP2-3; RRM1; SNRPF; STK32B; BDKRB1; ZBTB8OS; CDK7; POLR2D; TNFSF18; SEPTIN11; SHCBP1; NTMT1; KIF20B; IL7R; ASF1B; MAP3K7CL; PKP4; LMO7-AS1; CAVIN1; GEMIN4; ERCC2; FGF2; NCEH1; HS6ST1; RCL1; PUS1; UAP1; NCAPH; KRT18; ARHGAP11A; RFC2; POLQ; MT2A; AC007040.2; MRPL13; AL353751.1; SNHG3; FSTL1; SCIN; IER3; JADE1; SRSF3; HMOX2; C12orf45; RPL22L1; CTIF; TMC3; PDLIM1; NOP16; CDCA5; MARCHF3; CRIM1; SHLD3; TOMM40; AC125807.2; FOSL2; ARHGAP23; CITED2; SKA1; AC027237.5; RASSF2; BCYRN1; BIRC5; GTF2H2; SKA3; THBS1; SNAPC1; CALD1; SPINT2; PTS; LATS2; TK1; NOLC1; KAZN; VKORC1L1; CDC20; CSRP1; TUBB4B; PIEZO1; AC055839.2; UBE2S; AP000944.5; PRELID1; ATAD3A; ETS1; AFAP1; EBNA1BP2; HSPA4; AURKA; PTTG1; PRKAG2; CORO1C; C3orf52; ATP8B1; ARSJ; RANGAP1; RGS20; TRIP13; PALMD; EXOSC2; ADAM19; RIMKLB; MATN2; PRC1; TRMT6; WDR34; NRXN3; NUDCD1; RAB3B; MMS22L; SYDE1; MPP5; ARID5B; ALYREF; ZWINT; NME1; COTL1; TXNRD1; GLS; LRRC7; THOP1; UBE2C; TLX3; CUL4B; ENAH; PAK1IP1; CDH6; ANXA3; CYTOR; POLR1E; AL928654.4; DAZAP1; SRF; RAD23B; PET117; MYC; DIMT1; MTCL1; DLGAP5; PCID2; LOXL2; NUAK1; HACD2; MRPS17; TUBA1B; NSUN2; SNRPB; MRPL12; SMTN; CNN2; SLC16A3; FAM207A; NAA15; TLL1; FLNC; GRPEL1; ACTN4; HAUS6; HSPA14; PBK; SRSF7; NCAPG2; SNU13; TOE1; EIF2S1; E2F7; RIPK2; ZNF469; ACTN1; FBN2; TRAM2; ANLN; TUBA1C; SAMD4A; PDCD1LG2; HSPD1; NT5DC3; UCK2; CCT4; PM20D2; MRPL14; CCNYL1; NDUFAF2; HJURP; ARHGAP18; PDCD5; PADI2; LSM12; RRS1; HSPE1; EMG1; LTV1; NEK7; HCCS; BUB1; MYBBP1A; ZBTB18; MAMLD1; ANXA2; KRT80; EIF5A; PHLDA2; ADK; KIFC3; DUSP14; CCDC80; USP53; G3BP1; NDUFAF4; LASP1; STAMBPL1; SLC25A32; IMP4; TMEM237; TACC3; TIMM50; METAP1; ELAVL1; MYO1C; WDR89; ATAD3B; GNAI1; KPNA4; SMS; RGMB; SLC7A5; EPAS1; RECK; TPM1; DDX47; CLCF1; FOSL1; METRNL; IFRD2; PKN3; RBM14; TOM1L2; CAP1; EIF3J; YARS1; TAGLN2; CAPN2; LRRC59; FSTL3; PIP5K1A; ENO1; RSL1D1; KPNA3; WNT5A; SH3RF1; YARS2; WDR43; PALM2AKAP2; EIF1AX; GNL3; ANXA2P2; MCAM; HYI; KNSTRN; LYPD6; LIMS2; PARPBP; TOMM5; CORO1A; MIR22HG; MAK16; FAM83D; CBR3; BCAR3; ME2; TUBB; PCGF6; HNRNPA1P10; LMO7; DHCR24; NOP56; BCCIP; NUDC; DNTTIP2; MTMR12; CPA4; SGO2; MYL12B; RAB3IP; SCARB1; WDR62; MAP2K3; CEBPZ; DCAF13; FABP5; ADARB1; RANBP1; FAM72D; CYB5B; L3HYPDH; NCAPG; SEC14L1; C1QBP; LIMA1; MALT1; UTP18; SDHB; FH; TARS3; NUP88; IPO5; PPM1G; C18orf25; SNRPA1; PSG1; WDR1; CDC42EP1; PHF19; MICAL2; CCT2; NIFK; KPNA2; HNRNPH3; CTNNAL1; EPS8; RRM2; RRP9; NOL6; ACTR3; NPM1; SHROOM3; MYL12A; VSIR; ARL4A; DKC1; PTP4A2; C20orf27; UGP2; LDHA; PUS7; TTC27; NGF; MEST; CYCS; DDX21; GAR1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -706,26 +706,26 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.0000020944066603438</v>
+        <v>0.000000107966438332202</v>
       </c>
       <c r="C8">
-        <v>0.00000733042331120331</v>
+        <v>0.000000377882534162706</v>
       </c>
       <c r="D8">
-        <v>0.627256739718528</v>
+        <v>0.704975715167238</v>
       </c>
       <c r="E8">
-        <v>0.385082512680794</v>
+        <v>0.396839536019529</v>
       </c>
       <c r="F8">
-        <v>1.4811253577119</v>
+        <v>1.52330282167278</v>
       </c>
       <c r="G8">
-        <v>842</v>
+        <v>871</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FNDC5; MROH7; ZC3H12B; DGKB; DRAXIN; CACNB2; P2RX7; RAB3C; ZNF843; MYO7A; FNDC11; MAN1C1; AK8; ISLR; MARCHF11; EML5; VWA5A; CHRD; ESRRG; AC009506.2; AC100786.1; ZNF608; BMF; AC120049.1; NLGN3; UBA7; RET; ABHD14A-ACY1; TMEM130; AL137002.2; RAG1; AC244033.2; ZNF404; FAM184A; ADSS1; TMEM169; AL356599.1; ADAM22; AL590560.3; LOH12CR2; GPRC5C; SCN7A; PPP1R13B; AC074212.1; ELMO1; LINC02691; PLPPR5; SRP14-AS1; ASGR1; GSTO2; AC004951.4; ZSCAN23; APC2; CREBRF; SLCO2B1; SORCS1; CHRNB4; FAM227B; PROX1; PRRT1; ERMAP; DOC2A; CXXC4; LRRN3; SLC38A3; TSHZ2; VASH2; BEND5; GPHN; ITPR1; DLX6; SHOX2; CAMK1G; UNC79; GARNL3; AC011504.1; MAML3; P2RX6; SH3GL1P1; ZNF792; MROH6; ABCG1; RASA4; PLXNC1; TBX19; GPR158; AP001372.2; CHRNA7; NGFR; FOXO6; LINC02606; RIPOR3; AL096711.2; ZNF436-AS1; IL34; MIR600HG; TSPOAP1; ABCD2; PAQR8; YPEL4; SGMS1-AS1; CES3; AC097382.3; LINC00847; TSLP; MAFB; MANSC1; WDR31; TBC1D8; NTRK1; CHRM4; AL683813.2; SLC2A12; IL33; STRA6; AC009812.1; CNIH3; ZNF704; IQCN; HGFAC; TRIB2; B3GALT4; ANGPTL2; HTR2B; SOX5; ARHGEF37; AC027228.2; KLRG1; PCDHB18P; PIK3R3; GPR173; CHRNA3; ZNF277; EBF4; MXI1; KCTD12; SYT1; PCDHGA1; Z99129.4; KIF26B; OGDHL; MST1; ODAM; FBXL20; ZNF235; RASA4DP; PCDHGB2; SHD; ZNF441; RNF144A; AL365205.1; SYT17; LRP4; PRCD; DNASE1; PCDHB6; LRRC37A3; SLC35E2A; ELAVL2; MAST4; MEGF9; EDNRA; ASXL3; STAC; METTL7A; YPEL3; ATP7A; ADAMTS13; ZNF423; NYAP1; RNF122; ACE; SLC26A11; EPCAM-DT; BDNF-AS; STON1; SOX4; FAM167A; RAB7B; ZNF436; PRRT4; AC106895.2; FGF11; MSX2; GSTA4; RNF112; TRIM52; FRG1HP; TTC28; NTNG2; VSTM4; SETBP1; FAM110B; RBP1; UNC5B; ODF3B; IL17RC; GOLGA6L5P; AC106881.1; C1QTNF6; RCOR2; FOXO4; AL161729.1; PRICKLE1; ORAI3; CSPG4P5; THSD7A; MMP11; SAMD11; AC009113.1; AGAP2; TRAPPC6A; HECA; DUSP2; AC093010.2; RAB33A; BBC3; DEPTOR; TRANK1; DUSP10; SH3PXD2A; FAXDC2; ATP1A1-AS1; PTCHD4; BCAS3; TP53INP2; RIMBP2; RHOBTB1; TBX2-AS1; MFSD6; CALCOCO1; APBB3; LINC00324; ATP6V1FNB; ZFP90; ATP8A2; AC022007.1; PAXIP1-AS2; ADGRL1; SERPINF1; SLC16A9; SDK2; THRA; AKAP13; CACNG8; PIK3IP1; KIF26A; FOXO1; ATP8A1; LINC01518; STARD8; CD9; PRPH; CALY; TMOD1; HIF3A; ZCCHC24; AP003498.1; C14orf132; NTRK3; PCMTD1; DEPP1; STIM2; NOVA2; PCDHB10; CRYBG3; TRPS1; FANK1; AC093849.2; SERPING1; PHOX2B; PCDHGB7; AL078621.3; AL162458.1; PGBD5; SCN3A; NDRG4; KIAA1549; DNMT3A; DCHS1; MARCHF2; SMAD9; FAM171B; GRIA3; SESN3; MRAP2; OSER1-DT; PTPRM; PPFIBP1; WBP1; NCALD; TMEM35A; DGKI; PLEKHM3; SCG2; SAMD14; MYO1D; BBS1; CMPK2; PSD3; AC244197.3; AC010478.1; FAM117B; SFRP1; AL353746.1; DNAJC4; ZNF449; ZNF397; CX3CL1; TBX2; VSIG10L; DYRK1B; ACP5; FZD1; MFAP2; PTCH2; AC010931.1; CYGB; LMTK3; ZNF345; GNG2; VANGL2; LINC02593; CEP68; B3GNT9; CNTN1; GMIP; SCN2B; ZFP37; AZIN2; CHRNB1; TRIL; ZCWPW2; ATP9A; MMD; MYLIP; TP53INP1; PCDHB8; HID1; HDAC5; ARMC9; KLF13; CTSO; KLHL13; IL11RA; TLE3; TRIM24; TRO; PI4KAP1; MCC; FOXN3; KLHDC9; FRAT1; SH3BGR; PTPRN; CERK; WDR86; TMSB15B; HERC2P3; PTPRN2; ACVR1; CACNA1G; SNAI1; EPHB4; PTPN13; SLC10A4; GRK3; ING4; CPXM1; MTURN; SH3BGRL; CHD3; CELSR3; AC068700.1; NLGN4X; DUSP15; ZNF785; PPP3CA; MXD4</t>
+          <t>FNDC5; MROH7; DNM1P51; ZC3H12B; DGKB; DRAXIN; CACNB2; P2RX7; AC138646.1; C9orf50; CCT6B; ZNF843; MYO7A; U47924.2; FNDC11; AK8; ISLR; MARCHF11; EML5; VWA5A; CNTNAP2; CHRD; ESRRG; AC009506.2; ZNF608; AMTN; BMF; NLGN3; UBA7; TMEM130; AL137002.2; RAG1; AC244033.2; ZNF404; FAM184A; ADSS1; TMEM169; AL356599.1; ADAM22; AL590560.3; LOH12CR2; GPRC5C; SCN7A; ADGRB1; PPP1R13B; RPL23AP49; AC074212.1; ELMO1; LINC02691; SRP14-AS1; GSTO2; AC004951.4; ZSCAN23; CREBRF; SLCO2B1; SORCS1; EBF1; CHRNB4; FAM227B; PROX1; PRRT1; ERMAP; CXXC4; INTS6-AS1; LRRN3; SLC38A3; TSHZ2; HSPB8; VASH2; BEND5; ITPR1; NAIP; DLX6; SHOX2; CAMK1G; GARNL3; MAML3; P2RX6; AC016590.3; LONRF2; RBMS3-AS3; MROH6; DBP; ABCG1; RASA4; PLXNC1; TBX19; GPR158; FOXO6; LINC02606; RIPOR3; ZNF436-AS1; IL34; MIR600HG; TSPOAP1; ABCD2; PAQR8; YPEL4; SGMS1-AS1; CES3; CUL9; AC097382.3; LINC00847; TSLP; AC073111.4; MAFB; MANSC1; PKIA; KRBA2; WDR31; SHISA2; TPBGL; SEC31B; TBC1D8; CHRM4; AL683813.2; SLC2A12; IL33; STRA6; CCDC18-AS1; AC009812.1; CNIH3; ZNF704; IQCN; HGFAC; TRIB2; B3GALT4; ANGPTL2; HTR2B; SOX5; ARHGEF37; PCDH1; AC027228.2; PCDHB18P; PIK3R3; GPR173; FBXL8; CHRNA3; ZNF277; EBF4; MXI1; KCTD12; SYT1; PCDHGA1; Z99129.4; KIF26B; PGF; OGDHL; MST1; ODAM; FBXL20; ZNF235; RASA4DP; RASSF4; PCDHGB2; FRY; AL365205.1; SYT17; LRP4; PRCD; DNASE1; PCDHB6; RGMA; ARHGAP44; LRRC37A3; SLC35E2A; ELAVL2; EGLN3; MAST4; MEGF9; EDNRA; STAC; NTNG1; METTL7A; YPEL3; SLC37A3; ATP7A; ADAMTS13; ZNF423; NYAP1; RNF122; ACE; AC007406.5; SLC26A11; EPCAM-DT; BDNF-AS; STON1; SOX4; FAM167A; STON1-GTF2A1L; RAB7B; ZNF436; PRRT4; AC106895.2; MSX2; GSTA4; FRG1HP; TTC28; NTNG2; ABCG4; VSTM4; SETBP1; FAM110B; RBP1; UNC5B; ODF3B; IL17RC; GOLGA6L5P; AC106881.1; C1QTNF6; CARF; FOXO4; AL161729.1; ORAI3; CSPG4P5; KCNH5; MMP11; SAMD11; AC009113.1; AGAP2; TRAPPC6A; HECA; DUSP2; AC093010.2; GREM2; RAB33A; BBC3; DEPTOR; TMEM143; TTLL3; DUSP10; SH3PXD2A; FAXDC2; NEFL; PTCHD4; BCAS3; TP53INP2; RIMBP2; RHOBTB1; TBX2-AS1; STC1; MFSD6; CALCOCO1; APBB3; LINC00324; ATP6V1FNB; GABRA3; ATP8A2; AC022007.1; PAXIP1-AS2; SERPINF1; SEPSECS; SLC16A9; THBS4; PCDHA7; SDK2; THRA; AKAP13; CACNG8; PAN2; PIK3IP1; KIF26A; FOXO1; ATP8A1; LINC01518; STARD8; CD9; PRPH; CALY; HIF3A; ZCCHC24; RENBP; AP003498.1; C14orf132; NTRK3; PCMTD1; DEPP1; STIM2; NOVA2; PCDHB10; CRYBG3; TRPS1; PPP2R2B; FANK1; AC093849.2; SERPING1; PHOX2B; JUP; PAMR1; PCDHGB7; AL078621.3; GPER1; AL162458.1; SCN3A; NDRG4; KIAA1549; DNMT3A; DCHS1; RAB31; MARCHF2; SMAD9; FAM171B; GRIA3; SESN3; MRAP2; OSER1-DT; AL513534.3; PTPRM; PPFIBP1; WBP1; NCALD; TMEM35A; DGKI; PLEKHM3; SCG2; SAMD14; RANBP17; MYO1D; TPP1; CMPK2; PSD3; AC010478.1; FAM117B; SFRP1; AL353746.1; DNAJC4; ZNF449; CX3CL1; TBX2; VSIG10L; DYRK1B; RGS5; ACP5; FZD1; MFAP2; PTCH2; C12orf76; SLC9A3-AS1; SLC18B1; CYGB; LMTK3; ZNF345; VANGL2; LINC02593; SLC18A3; B3GNT9; GMIP; SCN2B; AZIN2; TRIL; ZCWPW2; ATP9A; MMD; MYLIP; TP53INP1; HDAC5; ARMC9; KLF13; CTSO; KLHL13; IL11RA; TLE3; TRIM24; KLF15; TRO; PI4KAP1; BAZ2B; FOXN3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
